--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136349030</v>
       </c>
       <c r="B4" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136349030</v>
       </c>
       <c r="B4" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136349030</v>
       </c>
       <c r="B4" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39622-2026 artfynd.xlsx
+++ b/artfynd/A 39622-2026 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>136583086</v>
       </c>
       <c r="B5" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
